--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middelhoog.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middelhoog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">

--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middelhoog.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middelhoog.xlsx
@@ -1065,7 +1065,7 @@
         <v>0.9548598516409671</v>
       </c>
       <c r="F27">
-        <v>0.5972269974804926</v>
+        <v>0.5972269974804925</v>
       </c>
       <c r="G27">
         <v>0.9402491716306757</v>
@@ -2963,7 +2963,7 @@
         <v>0.9844347611785202</v>
       </c>
       <c r="F100">
-        <v>1.529333126980017</v>
+        <v>1.529333126980018</v>
       </c>
       <c r="G100">
         <v>1.019264128699847</v>
@@ -3405,7 +3405,7 @@
         <v>0.8782870468847525</v>
       </c>
       <c r="F117">
-        <v>0.9490752879438371</v>
+        <v>0.949075287943837</v>
       </c>
       <c r="G117">
         <v>0.8652384345428338</v>
@@ -5381,7 +5381,7 @@
         <v>0.8089219547866827</v>
       </c>
       <c r="F193">
-        <v>1.232831673618838</v>
+        <v>1.232831673618839</v>
       </c>
       <c r="G193">
         <v>0.8333613252791724</v>
@@ -9125,7 +9125,7 @@
         <v>0.573983791824675</v>
       </c>
       <c r="F337">
-        <v>0.4848874116163825</v>
+        <v>0.4848874116163827</v>
       </c>
       <c r="G337">
         <v>0.574789220260741</v>
